--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251003_184627.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251003_184627.xlsx
@@ -5218,7 +5218,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5362,7 +5362,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5662,7 +5662,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251003_184627.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251003_184627.xlsx
@@ -5218,7 +5218,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5362,7 +5362,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5662,7 +5662,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7228,7 +7228,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251003_184627.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251003_184627.xlsx
@@ -5218,7 +5218,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5362,7 +5362,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5662,7 +5662,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7228,7 +7228,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251003_184627.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251003_184627.xlsx
@@ -7228,7 +7228,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251003_184627.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251003_184627.xlsx
@@ -7228,7 +7228,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251003_184627.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251003_184627.xlsx
@@ -5218,7 +5218,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5362,7 +5362,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5662,7 +5662,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
